--- a/imalat sanayi pmi.xlsx
+++ b/imalat sanayi pmi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omerozogul/Desktop/DashboardProje/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\splktfs\Aktif Pasif Yonetimi\Aktif Pasif\PARA PİYASALARI\Reports\APKO\APKO Veriler\github_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12037598-2F6C-654A-8C28-A3214852D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CD92EC-70C3-4D76-BFCA-7E314EC794D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" tabRatio="874" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28710" yWindow="-16440" windowWidth="29040" windowHeight="15720" tabRatio="874" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SÜ.PMI.KKO" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
   <si>
     <t>Tarih</t>
   </si>
@@ -171,9 +171,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,7 +211,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -317,7 +317,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -459,7 +459,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -470,15 +470,15 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I115"/>
+  <sheetFormatPr defaultColWidth="10.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.1640625" style="1"/>
+    <col min="1" max="1" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>42736</v>
       </c>
@@ -494,7 +494,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>42767</v>
       </c>
@@ -502,7 +502,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>42795</v>
       </c>
@@ -510,7 +510,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>42826</v>
       </c>
@@ -518,7 +518,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>42856</v>
       </c>
@@ -526,7 +526,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>42887</v>
       </c>
@@ -534,7 +534,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>42917</v>
       </c>
@@ -542,7 +542,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>42948</v>
       </c>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>42979</v>
       </c>
@@ -561,7 +561,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>43009</v>
       </c>
@@ -569,7 +569,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>43040</v>
       </c>
@@ -577,7 +577,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>43070</v>
       </c>
@@ -585,7 +585,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>43101</v>
       </c>
@@ -593,7 +593,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>43132</v>
       </c>
@@ -604,7 +604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>43160</v>
       </c>
@@ -612,7 +612,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>43191</v>
       </c>
@@ -620,7 +620,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>43221</v>
       </c>
@@ -628,7 +628,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>43252</v>
       </c>
@@ -636,7 +636,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>43282</v>
       </c>
@@ -647,7 +647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>43313</v>
       </c>
@@ -655,7 +655,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>43344</v>
       </c>
@@ -663,7 +663,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>43374</v>
       </c>
@@ -671,7 +671,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>43405</v>
       </c>
@@ -679,7 +679,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>43435</v>
       </c>
@@ -687,7 +687,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>43466</v>
       </c>
@@ -695,7 +695,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>43497</v>
       </c>
@@ -703,7 +703,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>43525</v>
       </c>
@@ -711,7 +711,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>43556</v>
       </c>
@@ -719,7 +719,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>43586</v>
       </c>
@@ -727,7 +727,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>43617</v>
       </c>
@@ -735,7 +735,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>43647</v>
       </c>
@@ -743,7 +743,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>43678</v>
       </c>
@@ -751,7 +751,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>43709</v>
       </c>
@@ -759,7 +759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>43739</v>
       </c>
@@ -767,7 +767,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>43770</v>
       </c>
@@ -775,7 +775,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>43800</v>
       </c>
@@ -783,7 +783,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>43831</v>
       </c>
@@ -791,7 +791,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>43862</v>
       </c>
@@ -799,7 +799,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>43891</v>
       </c>
@@ -807,7 +807,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>43922</v>
       </c>
@@ -815,7 +815,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>43952</v>
       </c>
@@ -823,7 +823,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>43983</v>
       </c>
@@ -831,7 +831,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>44013</v>
       </c>
@@ -839,7 +839,7 @@
         <v>56.9</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44044</v>
       </c>
@@ -847,7 +847,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>44075</v>
       </c>
@@ -855,7 +855,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>44105</v>
       </c>
@@ -863,7 +863,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>44136</v>
       </c>
@@ -871,7 +871,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>44166</v>
       </c>
@@ -879,7 +879,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>44197</v>
       </c>
@@ -887,7 +887,7 @@
         <v>54.4</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>44228</v>
       </c>
@@ -895,7 +895,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>44256</v>
       </c>
@@ -903,7 +903,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>44287</v>
       </c>
@@ -911,7 +911,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>44317</v>
       </c>
@@ -919,7 +919,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>44348</v>
       </c>
@@ -927,7 +927,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>44378</v>
       </c>
@@ -935,7 +935,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>44409</v>
       </c>
@@ -943,7 +943,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>44440</v>
       </c>
@@ -951,7 +951,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>44470</v>
       </c>
@@ -959,7 +959,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>44501</v>
       </c>
@@ -967,7 +967,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>44531</v>
       </c>
@@ -975,7 +975,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>44562</v>
       </c>
@@ -983,7 +983,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>44593</v>
       </c>
@@ -991,7 +991,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>44621</v>
       </c>
@@ -999,7 +999,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>44652</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>44682</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>44713</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>44743</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>44774</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>44805</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>44835</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>44866</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>44896</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>44927</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>44958</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>44986</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>45017</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>45047</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>45078</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>45108</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>45139</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>45170</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>45200</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>45231</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>45261</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>45292</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>45323</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>45352</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>45383</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>45413</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>45444</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>45474</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>45505</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>45536</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>45566</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>45597</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>45627</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>45658</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>45689</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>45717</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45748</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45778</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45809</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45839</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45870</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45901</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>45931</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>45962</v>
       </c>
@@ -1351,12 +1351,25 @@
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>45992</v>
       </c>
       <c r="B109" s="3">
         <v>48.9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B110" s="3">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1364,4 +1377,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ce47449c-aead-4773-aea9-0d789a4a6973}" enabled="1" method="Privileged" siteId="{a71b8764-0a7a-4511-8f04-04867f0718ab}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>